--- a/quizzes/peinture-14e.xlsx
+++ b/quizzes/peinture-14e.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836399DA-1C0D-4C6C-9E5D-1D35136272BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1126,9 +1132,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/2/2b/Giotto_-_Scrovegni_-_-13-_-_God_Sends_Gabriel_to_the_Virgin.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>https://fr.wikipedia.org/wiki/Chapelle_des_Scrovegni#/media/Fichier:Giotto_di_Bondone_-_No._14_Annunciation_-_The_Angel_Gabriel_Sent_by_God_-_WGA09190.jpg</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c4/Giotto_di_Bondone_-_No._15_Annunciation_-_The_Virgin_Receiving_the_Message_-_WGA09191.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -2021,13 +2024,16 @@
   </si>
   <si>
     <t>da FIRENZE</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/c/c7/Giotto_di_Bondone_-_No._14_Annunciation_-_The_Angel_Gabriel_Sent_by_God_-_WGA09190.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2072,18 +2078,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2121,7 +2135,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2155,6 +2169,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2189,9 +2204,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2364,11 +2380,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y119"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="13" max="13" width="41.28515625" customWidth="1"/>
+    <col min="16" max="16" width="38.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2445,7 +2465,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -2483,25 +2503,25 @@
         <v>345</v>
       </c>
       <c r="O2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Q2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="S2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="W2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X2">
         <v>2</v>
@@ -2510,7 +2530,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -2545,25 +2565,25 @@
         <v>346</v>
       </c>
       <c r="O3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="S3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="W3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X3">
         <v>2</v>
@@ -2572,7 +2592,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -2595,22 +2615,22 @@
         <v>347</v>
       </c>
       <c r="O4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="S4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="U4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="W4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="X4">
         <v>3</v>
@@ -2619,7 +2639,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -2642,22 +2662,22 @@
         <v>348</v>
       </c>
       <c r="O5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="S5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="U5" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="W5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="X5">
         <v>3</v>
@@ -2666,7 +2686,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -2695,22 +2715,22 @@
         <v>349</v>
       </c>
       <c r="O6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="S6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="U6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="W6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X6">
         <v>3</v>
@@ -2719,7 +2739,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -2751,10 +2771,10 @@
         <v>350</v>
       </c>
       <c r="S7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="W7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X7">
         <v>3</v>
@@ -2763,7 +2783,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -2792,19 +2812,19 @@
         <v>351</v>
       </c>
       <c r="Q8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="S8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T8" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="U8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="W8" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X8">
         <v>3</v>
@@ -2813,7 +2833,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -2845,13 +2865,13 @@
         <v>352</v>
       </c>
       <c r="Q9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="S9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="W9" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X9">
         <v>3</v>
@@ -2860,7 +2880,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2892,28 +2912,28 @@
         <v>353</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="S10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="U10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="W10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X10">
         <v>3</v>
       </c>
       <c r="Y10" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -2945,28 +2965,28 @@
         <v>354</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="S11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T11" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="U11" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="W11" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X11">
         <v>3</v>
       </c>
       <c r="Y11" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -2998,28 +3018,28 @@
         <v>355</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="S12" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T12" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="U12" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="W12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X12">
         <v>3</v>
       </c>
       <c r="Y12" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -3051,25 +3071,25 @@
         <v>356</v>
       </c>
       <c r="O13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="S13" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T13" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U13" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W13" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X13">
         <v>1</v>
@@ -3078,7 +3098,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -3116,25 +3136,25 @@
         <v>357</v>
       </c>
       <c r="O14" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="S14" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T14" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U14" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W14" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X14">
         <v>1</v>
@@ -3143,7 +3163,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -3178,25 +3198,25 @@
         <v>358</v>
       </c>
       <c r="O15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="S15" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T15" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W15" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -3205,7 +3225,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -3240,25 +3260,25 @@
         <v>359</v>
       </c>
       <c r="O16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q16" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="S16" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T16" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U16" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W16" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -3267,7 +3287,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3302,25 +3322,25 @@
         <v>360</v>
       </c>
       <c r="O17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="S17" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T17" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U17" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X17">
         <v>1</v>
@@ -3329,7 +3349,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -3364,25 +3384,25 @@
         <v>361</v>
       </c>
       <c r="O18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q18" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="S18" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T18" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U18" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X18">
         <v>1</v>
@@ -3391,7 +3411,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -3426,25 +3446,25 @@
         <v>362</v>
       </c>
       <c r="O19" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q19" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="S19" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T19" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U19" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W19" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X19">
         <v>1</v>
@@ -3453,7 +3473,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -3488,25 +3508,25 @@
         <v>363</v>
       </c>
       <c r="O20" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q20" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="S20" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T20" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U20" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W20" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X20">
         <v>1</v>
@@ -3515,7 +3535,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -3550,25 +3570,25 @@
         <v>364</v>
       </c>
       <c r="O21" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q21" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S21" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T21" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U21" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W21" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X21">
         <v>1</v>
@@ -3577,7 +3597,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -3612,25 +3632,25 @@
         <v>365</v>
       </c>
       <c r="O22" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S22" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T22" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U22" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W22" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -3639,7 +3659,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -3674,25 +3694,25 @@
         <v>366</v>
       </c>
       <c r="O23" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q23" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="S23" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T23" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U23" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W23" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X23">
         <v>1</v>
@@ -3701,7 +3721,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -3736,25 +3756,25 @@
         <v>367</v>
       </c>
       <c r="O24" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="S24" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T24" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U24" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W24" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X24">
         <v>1</v>
@@ -3763,7 +3783,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3798,25 +3818,25 @@
         <v>368</v>
       </c>
       <c r="O25" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q25" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="S25" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T25" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U25" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W25" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X25">
         <v>1</v>
@@ -3825,7 +3845,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -3860,25 +3880,25 @@
         <v>369</v>
       </c>
       <c r="O26" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q26" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="S26" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T26" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U26" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W26" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X26">
         <v>1</v>
@@ -3887,7 +3907,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -3919,28 +3939,28 @@
         <v>260</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>370</v>
+        <v>668</v>
       </c>
       <c r="O27" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q27" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="S27" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T27" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U27" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W27" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X27">
         <v>1</v>
@@ -3949,7 +3969,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -3981,34 +4001,34 @@
         <v>261</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O28" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q28" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="S28" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T28" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U28" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W28" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="Y28" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -4040,28 +4060,28 @@
         <v>262</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O29" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q29" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="S29" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T29" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U29" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W29" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X29">
         <v>1</v>
@@ -4070,7 +4090,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -4102,28 +4122,28 @@
         <v>263</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O30" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q30" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="S30" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T30" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U30" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W30" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X30">
         <v>1</v>
@@ -4132,7 +4152,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -4164,28 +4184,28 @@
         <v>264</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O31" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q31" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S31" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T31" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U31" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W31" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X31">
         <v>1</v>
@@ -4194,7 +4214,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -4226,28 +4246,28 @@
         <v>265</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O32" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q32" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S32" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T32" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U32" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W32" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X32">
         <v>1</v>
@@ -4256,7 +4276,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -4288,28 +4308,28 @@
         <v>266</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O33" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q33" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S33" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T33" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U33" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W33" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X33">
         <v>1</v>
@@ -4318,7 +4338,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -4350,28 +4370,28 @@
         <v>267</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O34" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q34" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S34" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T34" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U34" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W34" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -4380,7 +4400,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -4412,28 +4432,28 @@
         <v>268</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O35" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q35" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S35" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T35" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U35" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W35" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X35">
         <v>1</v>
@@ -4442,7 +4462,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -4474,28 +4494,28 @@
         <v>269</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O36" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q36" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S36" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T36" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U36" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W36" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X36">
         <v>1</v>
@@ -4504,7 +4524,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -4536,28 +4556,28 @@
         <v>270</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O37" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q37" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="S37" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T37" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U37" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W37" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X37">
         <v>1</v>
@@ -4566,7 +4586,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -4598,28 +4618,28 @@
         <v>271</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O38" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q38" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="S38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T38" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U38" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W38" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X38">
         <v>1</v>
@@ -4628,7 +4648,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -4660,28 +4680,28 @@
         <v>272</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O39" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q39" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="S39" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T39" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U39" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W39" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X39">
         <v>1</v>
@@ -4690,7 +4710,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>32</v>
       </c>
@@ -4722,28 +4742,28 @@
         <v>273</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O40" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q40" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="S40" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T40" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U40" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W40" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X40">
         <v>1</v>
@@ -4752,7 +4772,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -4784,28 +4804,28 @@
         <v>274</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O41" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q41" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="S41" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T41" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="U41" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="W41" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X41">
         <v>1</v>
@@ -4814,7 +4834,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -4846,28 +4866,28 @@
         <v>275</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O42" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="S42" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T42" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U42" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W42" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X42">
         <v>1</v>
@@ -4876,7 +4896,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>32</v>
       </c>
@@ -4908,28 +4928,28 @@
         <v>276</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O43" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q43" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="S43" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T43" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U43" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W43" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X43">
         <v>1</v>
@@ -4938,7 +4958,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>32</v>
       </c>
@@ -4970,28 +4990,28 @@
         <v>277</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O44" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q44" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="S44" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T44" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U44" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W44" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X44">
         <v>1</v>
@@ -5000,7 +5020,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>32</v>
       </c>
@@ -5032,28 +5052,28 @@
         <v>278</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="O45" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q45" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="S45" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T45" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U45" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W45" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X45">
         <v>1</v>
@@ -5062,7 +5082,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>32</v>
       </c>
@@ -5094,28 +5114,28 @@
         <v>279</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O46" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q46" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S46" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T46" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U46" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W46" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X46">
         <v>1</v>
@@ -5124,7 +5144,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>32</v>
       </c>
@@ -5156,28 +5176,28 @@
         <v>280</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O47" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q47" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="S47" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T47" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U47" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W47" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X47">
         <v>1</v>
@@ -5186,7 +5206,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>32</v>
       </c>
@@ -5218,28 +5238,28 @@
         <v>281</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="O48" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q48" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="S48" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T48" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U48" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W48" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X48">
         <v>1</v>
@@ -5248,7 +5268,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>32</v>
       </c>
@@ -5280,28 +5300,28 @@
         <v>282</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O49" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q49" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="S49" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T49" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U49" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W49" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X49">
         <v>1</v>
@@ -5310,7 +5330,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>32</v>
       </c>
@@ -5345,28 +5365,28 @@
         <v>283</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O50" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q50" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="S50" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T50" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U50" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W50" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X50">
         <v>1</v>
@@ -5375,7 +5395,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>32</v>
       </c>
@@ -5410,28 +5430,28 @@
         <v>284</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O51" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q51" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="S51" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T51" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U51" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="W51" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X51">
         <v>1</v>
@@ -5440,7 +5460,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -5472,28 +5492,28 @@
         <v>285</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O52" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q52" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="S52" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T52" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U52" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W52" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -5502,7 +5522,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>32</v>
       </c>
@@ -5534,28 +5554,28 @@
         <v>286</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O53" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q53" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="S53" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T53" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U53" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W53" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X53">
         <v>1</v>
@@ -5564,7 +5584,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>32</v>
       </c>
@@ -5596,28 +5616,28 @@
         <v>287</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O54" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q54" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="S54" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T54" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U54" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W54" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X54">
         <v>1</v>
@@ -5626,7 +5646,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>32</v>
       </c>
@@ -5658,28 +5678,28 @@
         <v>288</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O55" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q55" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="S55" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T55" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U55" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W55" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X55">
         <v>1</v>
@@ -5688,7 +5708,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>32</v>
       </c>
@@ -5720,28 +5740,28 @@
         <v>289</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O56" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="S56" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T56" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U56" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W56" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X56">
         <v>1</v>
@@ -5750,7 +5770,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -5782,28 +5802,28 @@
         <v>290</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O57" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q57" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="S57" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T57" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U57" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X57">
         <v>1</v>
@@ -5812,7 +5832,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -5844,28 +5864,28 @@
         <v>291</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O58" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q58" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="S58" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T58" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U58" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W58" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X58">
         <v>1</v>
@@ -5874,7 +5894,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -5906,28 +5926,28 @@
         <v>292</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O59" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q59" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="S59" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T59" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U59" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W59" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X59">
         <v>1</v>
@@ -5936,7 +5956,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>32</v>
       </c>
@@ -5968,28 +5988,28 @@
         <v>293</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="O60" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q60" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="S60" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T60" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U60" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W60" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X60">
         <v>1</v>
@@ -5998,7 +6018,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>32</v>
       </c>
@@ -6030,28 +6050,28 @@
         <v>294</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="O61" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q61" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="S61" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T61" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U61" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W61" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X61">
         <v>1</v>
@@ -6060,7 +6080,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>32</v>
       </c>
@@ -6092,28 +6112,28 @@
         <v>295</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="O62" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q62" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="S62" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T62" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U62" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W62" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X62">
         <v>1</v>
@@ -6122,7 +6142,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>32</v>
       </c>
@@ -6154,28 +6174,28 @@
         <v>296</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="O63" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q63" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="S63" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T63" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U63" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W63" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X63">
         <v>1</v>
@@ -6184,7 +6204,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>32</v>
       </c>
@@ -6216,28 +6236,28 @@
         <v>297</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="O64" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q64" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="S64" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T64" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U64" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W64" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X64">
         <v>1</v>
@@ -6246,7 +6266,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>32</v>
       </c>
@@ -6278,28 +6298,28 @@
         <v>298</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="O65" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q65" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="S65" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T65" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="U65" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="W65" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X65">
         <v>1</v>
@@ -6308,7 +6328,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>32</v>
       </c>
@@ -6340,25 +6360,25 @@
         <v>299</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O66" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Q66" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="S66" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T66" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="U66" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="W66" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X66">
         <v>1</v>
@@ -6367,7 +6387,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>33</v>
       </c>
@@ -6396,22 +6416,22 @@
         <v>300</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q67" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="S67" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T67" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="U67" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="W67" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X67">
         <v>1</v>
@@ -6420,7 +6440,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>33</v>
       </c>
@@ -6449,34 +6469,34 @@
         <v>300</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="O68" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q68" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="S68" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T68" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="U68" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="W68" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>33</v>
       </c>
@@ -6505,34 +6525,34 @@
         <v>301</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O69" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q69" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="S69" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T69" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="U69" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="W69" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X69">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>33</v>
       </c>
@@ -6561,34 +6581,34 @@
         <v>302</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O70" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q70" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="S70" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T70" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="U70" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="W70" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X70">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>33</v>
       </c>
@@ -6617,34 +6637,34 @@
         <v>270</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O71" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q71" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="S71" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T71" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="U71" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="W71" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>33</v>
       </c>
@@ -6673,34 +6693,34 @@
         <v>303</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="O72" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q72" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="S72" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T72" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="U72" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="W72" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>33</v>
       </c>
@@ -6729,34 +6749,34 @@
         <v>304</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O73" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q73" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="S73" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T73" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="U73" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="W73" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>33</v>
       </c>
@@ -6785,34 +6805,34 @@
         <v>305</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O74" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q74" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="S74" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T74" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="U74" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="W74" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>33</v>
       </c>
@@ -6841,34 +6861,34 @@
         <v>271</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O75" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q75" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="S75" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T75" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="U75" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="W75" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X75">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -6900,25 +6920,25 @@
         <v>306</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q76" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="S76" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T76" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="U76" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="W76" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X76">
         <v>1</v>
@@ -6927,7 +6947,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>34</v>
       </c>
@@ -6950,25 +6970,25 @@
         <v>299</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q77" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="S77" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T77" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="U77" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="W77" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X77">
         <v>1</v>
@@ -6977,7 +6997,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>35</v>
       </c>
@@ -7006,22 +7026,22 @@
         <v>307</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="S78" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T78" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="U78" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="W78" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X78">
         <v>2</v>
@@ -7030,7 +7050,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>36</v>
       </c>
@@ -7056,25 +7076,25 @@
         <v>308</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q79" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="S79" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T79" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="U79" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="W79" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X79">
         <v>1</v>
@@ -7083,7 +7103,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>36</v>
       </c>
@@ -7109,25 +7129,25 @@
         <v>309</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q80" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="S80" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T80" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="U80" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="W80" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X80">
         <v>1</v>
@@ -7136,7 +7156,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>36</v>
       </c>
@@ -7162,25 +7182,25 @@
         <v>310</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O81" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q81" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="S81" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="U81" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="W81" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X81">
         <v>1</v>
@@ -7189,7 +7209,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>36</v>
       </c>
@@ -7215,25 +7235,25 @@
         <v>311</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q82" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="S82" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T82" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="U82" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="W82" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X82">
         <v>1</v>
@@ -7242,7 +7262,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>36</v>
       </c>
@@ -7268,25 +7288,25 @@
         <v>312</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q83" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="S83" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T83" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="U83" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="W83" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X83">
         <v>1</v>
@@ -7295,7 +7315,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>36</v>
       </c>
@@ -7321,25 +7341,25 @@
         <v>313</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q84" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="S84" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T84" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="U84" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="W84" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X84">
         <v>1</v>
@@ -7348,7 +7368,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>36</v>
       </c>
@@ -7374,25 +7394,25 @@
         <v>314</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q85" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="S85" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T85" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="U85" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="W85" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X85">
         <v>1</v>
@@ -7401,7 +7421,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>36</v>
       </c>
@@ -7430,25 +7450,25 @@
         <v>315</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="O86" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="S86" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T86" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="U86" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="W86" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X86">
         <v>1</v>
@@ -7457,7 +7477,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>36</v>
       </c>
@@ -7486,25 +7506,25 @@
         <v>316</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="O87" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="S87" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T87" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="U87" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="W87" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X87">
         <v>1</v>
@@ -7513,7 +7533,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>36</v>
       </c>
@@ -7539,25 +7559,25 @@
         <v>317</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q88" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="S88" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T88" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="U88" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="W88" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X88">
         <v>1</v>
@@ -7566,7 +7586,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>36</v>
       </c>
@@ -7595,28 +7615,28 @@
         <v>318</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O89" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q89" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="S89" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T89" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U89" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="W89" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X89">
         <v>1</v>
@@ -7625,7 +7645,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>36</v>
       </c>
@@ -7654,28 +7674,28 @@
         <v>319</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O90" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q90" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="S90" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T90" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U90" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="W90" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X90">
         <v>1</v>
@@ -7684,7 +7704,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>36</v>
       </c>
@@ -7713,28 +7733,28 @@
         <v>320</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O91" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q91" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="S91" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T91" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U91" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="W91" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X91">
         <v>1</v>
@@ -7743,7 +7763,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>36</v>
       </c>
@@ -7772,28 +7792,28 @@
         <v>321</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O92" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q92" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="S92" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T92" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="U92" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="W92" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X92">
         <v>1</v>
@@ -7802,7 +7822,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>37</v>
       </c>
@@ -7828,25 +7848,25 @@
         <v>322</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q93" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="S93" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T93" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="U93" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="W93" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X93">
         <v>1</v>
@@ -7855,7 +7875,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>37</v>
       </c>
@@ -7881,28 +7901,28 @@
         <v>323</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O94" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q94" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="S94" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T94" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="U94" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="W94" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X94">
         <v>1</v>
@@ -7911,7 +7931,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>37</v>
       </c>
@@ -7937,28 +7957,28 @@
         <v>324</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O95" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q95" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="S95" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T95" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="U95" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="W95" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X95">
         <v>1</v>
@@ -7967,7 +7987,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>37</v>
       </c>
@@ -7993,25 +8013,25 @@
         <v>325</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q96" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="S96" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T96" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="U96" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="W96" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X96">
         <v>1</v>
@@ -8020,7 +8040,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>37</v>
       </c>
@@ -8046,28 +8066,28 @@
         <v>326</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="O97" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q97" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="S97" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T97" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="U97" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="W97" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X97">
         <v>1</v>
@@ -8076,7 +8096,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>37</v>
       </c>
@@ -8102,25 +8122,25 @@
         <v>325</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q98" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="S98" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T98" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="U98" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="W98" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X98">
         <v>1</v>
@@ -8129,7 +8149,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>37</v>
       </c>
@@ -8155,28 +8175,28 @@
         <v>327</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="O99" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q99" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="S99" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T99" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="U99" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="W99" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X99">
         <v>1</v>
@@ -8185,7 +8205,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>37</v>
       </c>
@@ -8211,28 +8231,28 @@
         <v>328</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="O100" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="P100" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q100" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="S100" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T100" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="U100" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="W100" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X100">
         <v>1</v>
@@ -8241,7 +8261,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>37</v>
       </c>
@@ -8270,25 +8290,25 @@
         <v>328</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O101" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="S101" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T101" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="U101" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="W101" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X101">
         <v>1</v>
@@ -8297,7 +8317,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>37</v>
       </c>
@@ -8323,22 +8343,22 @@
         <v>329</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O102" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q102" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="S102" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="W102" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X102">
         <v>1</v>
@@ -8347,7 +8367,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>38</v>
       </c>
@@ -8373,25 +8393,25 @@
         <v>330</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="P103" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q103" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="S103" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T103" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="U103" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="W103" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X103">
         <v>1</v>
@@ -8400,7 +8420,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>39</v>
       </c>
@@ -8423,25 +8443,25 @@
         <v>331</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q104" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="S104" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T104" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="U104" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="W104" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X104">
         <v>1</v>
@@ -8450,7 +8470,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -8476,28 +8496,28 @@
         <v>332</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="P105" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q105" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="R105" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="S105" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T105" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="U105" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="W105" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X105">
         <v>1</v>
@@ -8506,7 +8526,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -8532,25 +8552,25 @@
         <v>242</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P106" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q106" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="S106" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T106" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="U106" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="W106" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X106">
         <v>1</v>
@@ -8559,7 +8579,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -8585,28 +8605,28 @@
         <v>333</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P107" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q107" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="R107" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="S107" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T107" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="U107" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="W107" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X107">
         <v>1</v>
@@ -8615,7 +8635,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -8641,28 +8661,28 @@
         <v>334</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P108" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q108" t="s">
         <v>334</v>
       </c>
       <c r="R108" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="S108" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T108" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="U108" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="W108" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X108">
         <v>1</v>
@@ -8671,7 +8691,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -8697,31 +8717,31 @@
         <v>335</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="O109" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q109" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="R109" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="S109" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T109" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U109" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="W109" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X109">
         <v>1</v>
@@ -8730,7 +8750,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -8756,31 +8776,31 @@
         <v>336</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="O110" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P110" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q110" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="R110" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="S110" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T110" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U110" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="W110" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X110">
         <v>1</v>
@@ -8789,7 +8809,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -8815,31 +8835,31 @@
         <v>337</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="O111" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q111" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="R111" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="S111" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T111" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U111" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="W111" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X111">
         <v>1</v>
@@ -8848,7 +8868,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -8874,28 +8894,28 @@
         <v>338</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P112" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q112" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="R112" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="S112" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T112" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="U112" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="W112" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X112">
         <v>1</v>
@@ -8904,7 +8924,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -8930,28 +8950,28 @@
         <v>339</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q113" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R113" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="S113" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T113" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="U113" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="W113" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X113">
         <v>1</v>
@@ -8960,7 +8980,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -8989,28 +9009,28 @@
         <v>340</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q114" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="R114" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="S114" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="T114" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="U114" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="W114" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X114">
         <v>1</v>
@@ -9019,7 +9039,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -9048,31 +9068,31 @@
         <v>257</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O115" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P115" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q115" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R115" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="S115" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T115" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="U115" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="W115" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X115">
         <v>1</v>
@@ -9081,7 +9101,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>41</v>
       </c>
@@ -9104,16 +9124,16 @@
         <v>341</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O116" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="S116" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="W116" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="X116">
         <v>3</v>
@@ -9122,7 +9142,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>42</v>
       </c>
@@ -9145,16 +9165,16 @@
         <v>342</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q117" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="S117" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="W117" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="X117">
         <v>3</v>
@@ -9163,7 +9183,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>43</v>
       </c>
@@ -9183,16 +9203,16 @@
         <v>343</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q118" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="S118" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="W118" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="X118">
         <v>2</v>
@@ -9201,7 +9221,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D119" t="s">
         <v>67</v>
       </c>
@@ -9218,22 +9238,22 @@
         <v>344</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q119" t="s">
+        <v>582</v>
+      </c>
+      <c r="S119" t="s">
         <v>583</v>
       </c>
-      <c r="S119" t="s">
-        <v>584</v>
-      </c>
       <c r="T119" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="U119" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="W119" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="X119">
         <v>3</v>
@@ -9241,245 +9261,245 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="K2" r:id="rId2"/>
-    <hyperlink ref="N2" r:id="rId3"/>
-    <hyperlink ref="P2" r:id="rId4"/>
-    <hyperlink ref="K3" r:id="rId5"/>
-    <hyperlink ref="N3" r:id="rId6"/>
-    <hyperlink ref="P3" r:id="rId7"/>
-    <hyperlink ref="N4" r:id="rId8"/>
-    <hyperlink ref="P4" r:id="rId9"/>
-    <hyperlink ref="N5" r:id="rId10"/>
-    <hyperlink ref="P5" r:id="rId11"/>
-    <hyperlink ref="N6" r:id="rId12"/>
-    <hyperlink ref="N7" r:id="rId13"/>
-    <hyperlink ref="N8" r:id="rId14"/>
-    <hyperlink ref="K9" r:id="rId15"/>
-    <hyperlink ref="N9" r:id="rId16"/>
-    <hyperlink ref="K10" r:id="rId17"/>
-    <hyperlink ref="N10" r:id="rId18"/>
-    <hyperlink ref="P10" r:id="rId19"/>
-    <hyperlink ref="K11" r:id="rId20"/>
-    <hyperlink ref="N11" r:id="rId21"/>
-    <hyperlink ref="P11" r:id="rId22"/>
-    <hyperlink ref="K12" r:id="rId23"/>
-    <hyperlink ref="N12" r:id="rId24"/>
-    <hyperlink ref="P12" r:id="rId25"/>
-    <hyperlink ref="N13" r:id="rId26"/>
-    <hyperlink ref="P13" r:id="rId27"/>
-    <hyperlink ref="K14" r:id="rId28"/>
-    <hyperlink ref="N14" r:id="rId29"/>
-    <hyperlink ref="P14" r:id="rId30"/>
-    <hyperlink ref="N15" r:id="rId31"/>
-    <hyperlink ref="P15" r:id="rId32"/>
-    <hyperlink ref="N16" r:id="rId33"/>
-    <hyperlink ref="P16" r:id="rId34"/>
-    <hyperlink ref="N17" r:id="rId35"/>
-    <hyperlink ref="P17" r:id="rId36"/>
-    <hyperlink ref="N18" r:id="rId37"/>
-    <hyperlink ref="P18" r:id="rId38"/>
-    <hyperlink ref="N19" r:id="rId39"/>
-    <hyperlink ref="P19" r:id="rId40"/>
-    <hyperlink ref="N20" r:id="rId41"/>
-    <hyperlink ref="P20" r:id="rId42"/>
-    <hyperlink ref="N21" r:id="rId43"/>
-    <hyperlink ref="P21" r:id="rId44"/>
-    <hyperlink ref="N22" r:id="rId45"/>
-    <hyperlink ref="P22" r:id="rId46"/>
-    <hyperlink ref="N23" r:id="rId47"/>
-    <hyperlink ref="P23" r:id="rId48"/>
-    <hyperlink ref="N24" r:id="rId49"/>
-    <hyperlink ref="P24" r:id="rId50"/>
-    <hyperlink ref="N25" r:id="rId51"/>
-    <hyperlink ref="P25" r:id="rId52"/>
-    <hyperlink ref="N26" r:id="rId53"/>
-    <hyperlink ref="P26" r:id="rId54"/>
-    <hyperlink ref="N27" r:id="rId55" location="/media/Fichier:Giotto_di_Bondone_-_No._14_Annunciation_-_The_Angel_Gabriel_Sent_by_God_-_WGA09190.jpg"/>
-    <hyperlink ref="P27" r:id="rId56"/>
-    <hyperlink ref="N28" r:id="rId57"/>
-    <hyperlink ref="P28" r:id="rId58"/>
-    <hyperlink ref="N29" r:id="rId59"/>
-    <hyperlink ref="P29" r:id="rId60"/>
-    <hyperlink ref="N30" r:id="rId61"/>
-    <hyperlink ref="P30" r:id="rId62"/>
-    <hyperlink ref="N31" r:id="rId63"/>
-    <hyperlink ref="P31" r:id="rId64"/>
-    <hyperlink ref="N32" r:id="rId65"/>
-    <hyperlink ref="P32" r:id="rId66"/>
-    <hyperlink ref="N33" r:id="rId67"/>
-    <hyperlink ref="P33" r:id="rId68"/>
-    <hyperlink ref="N34" r:id="rId69"/>
-    <hyperlink ref="P34" r:id="rId70"/>
-    <hyperlink ref="N35" r:id="rId71"/>
-    <hyperlink ref="P35" r:id="rId72"/>
-    <hyperlink ref="N36" r:id="rId73"/>
-    <hyperlink ref="P36" r:id="rId74"/>
-    <hyperlink ref="N37" r:id="rId75"/>
-    <hyperlink ref="P37" r:id="rId76"/>
-    <hyperlink ref="N38" r:id="rId77"/>
-    <hyperlink ref="P38" r:id="rId78"/>
-    <hyperlink ref="N39" r:id="rId79"/>
-    <hyperlink ref="P39" r:id="rId80"/>
-    <hyperlink ref="N40" r:id="rId81"/>
-    <hyperlink ref="P40" r:id="rId82"/>
-    <hyperlink ref="N41" r:id="rId83"/>
-    <hyperlink ref="P41" r:id="rId84"/>
-    <hyperlink ref="N42" r:id="rId85"/>
-    <hyperlink ref="P42" r:id="rId86"/>
-    <hyperlink ref="N43" r:id="rId87"/>
-    <hyperlink ref="P43" r:id="rId88"/>
-    <hyperlink ref="N44" r:id="rId89"/>
-    <hyperlink ref="P44" r:id="rId90"/>
-    <hyperlink ref="N45" r:id="rId91"/>
-    <hyperlink ref="P45" r:id="rId92"/>
-    <hyperlink ref="N46" r:id="rId93"/>
-    <hyperlink ref="P46" r:id="rId94"/>
-    <hyperlink ref="N47" r:id="rId95"/>
-    <hyperlink ref="P47" r:id="rId96"/>
-    <hyperlink ref="N48" r:id="rId97"/>
-    <hyperlink ref="P48" r:id="rId98"/>
-    <hyperlink ref="N49" r:id="rId99"/>
-    <hyperlink ref="P49" r:id="rId100"/>
-    <hyperlink ref="K50" r:id="rId101"/>
-    <hyperlink ref="N50" r:id="rId102"/>
-    <hyperlink ref="P50" r:id="rId103"/>
-    <hyperlink ref="K51" r:id="rId104"/>
-    <hyperlink ref="N51" r:id="rId105"/>
-    <hyperlink ref="P51" r:id="rId106"/>
-    <hyperlink ref="N52" r:id="rId107"/>
-    <hyperlink ref="P52" r:id="rId108"/>
-    <hyperlink ref="N53" r:id="rId109"/>
-    <hyperlink ref="P53" r:id="rId110"/>
-    <hyperlink ref="N54" r:id="rId111"/>
-    <hyperlink ref="P54" r:id="rId112"/>
-    <hyperlink ref="N55" r:id="rId113"/>
-    <hyperlink ref="P55" r:id="rId114"/>
-    <hyperlink ref="N56" r:id="rId115"/>
-    <hyperlink ref="P56" r:id="rId116"/>
-    <hyperlink ref="N57" r:id="rId117"/>
-    <hyperlink ref="P57" r:id="rId118"/>
-    <hyperlink ref="N58" r:id="rId119"/>
-    <hyperlink ref="P58" r:id="rId120"/>
-    <hyperlink ref="N59" r:id="rId121"/>
-    <hyperlink ref="P59" r:id="rId122"/>
-    <hyperlink ref="N60" r:id="rId123"/>
-    <hyperlink ref="P60" r:id="rId124"/>
-    <hyperlink ref="N61" r:id="rId125"/>
-    <hyperlink ref="P61" r:id="rId126"/>
-    <hyperlink ref="N62" r:id="rId127"/>
-    <hyperlink ref="P62" r:id="rId128"/>
-    <hyperlink ref="N63" r:id="rId129"/>
-    <hyperlink ref="P63" r:id="rId130"/>
-    <hyperlink ref="N64" r:id="rId131"/>
-    <hyperlink ref="P64" r:id="rId132"/>
-    <hyperlink ref="N65" r:id="rId133"/>
-    <hyperlink ref="P65" r:id="rId134"/>
-    <hyperlink ref="N66" r:id="rId135"/>
-    <hyperlink ref="N67" r:id="rId136"/>
-    <hyperlink ref="N68" r:id="rId137"/>
-    <hyperlink ref="P68" r:id="rId138"/>
-    <hyperlink ref="N69" r:id="rId139"/>
-    <hyperlink ref="P69" r:id="rId140"/>
-    <hyperlink ref="N70" r:id="rId141"/>
-    <hyperlink ref="P70" r:id="rId142"/>
-    <hyperlink ref="N71" r:id="rId143"/>
-    <hyperlink ref="P71" r:id="rId144"/>
-    <hyperlink ref="N72" r:id="rId145"/>
-    <hyperlink ref="P72" r:id="rId146"/>
-    <hyperlink ref="N73" r:id="rId147"/>
-    <hyperlink ref="P73" r:id="rId148"/>
-    <hyperlink ref="N74" r:id="rId149"/>
-    <hyperlink ref="P74" r:id="rId150"/>
-    <hyperlink ref="N75" r:id="rId151"/>
-    <hyperlink ref="P75" r:id="rId152"/>
-    <hyperlink ref="N76" r:id="rId153"/>
-    <hyperlink ref="P76" r:id="rId154"/>
-    <hyperlink ref="N77" r:id="rId155"/>
-    <hyperlink ref="P77" r:id="rId156"/>
-    <hyperlink ref="N78" r:id="rId157"/>
-    <hyperlink ref="P78" r:id="rId158"/>
-    <hyperlink ref="N79" r:id="rId159"/>
-    <hyperlink ref="P79" r:id="rId160"/>
-    <hyperlink ref="N80" r:id="rId161"/>
-    <hyperlink ref="P80" r:id="rId162"/>
-    <hyperlink ref="N81" r:id="rId163"/>
-    <hyperlink ref="P81" r:id="rId164"/>
-    <hyperlink ref="N82" r:id="rId165"/>
-    <hyperlink ref="P82" r:id="rId166"/>
-    <hyperlink ref="N83" r:id="rId167"/>
-    <hyperlink ref="P83" r:id="rId168"/>
-    <hyperlink ref="N84" r:id="rId169"/>
-    <hyperlink ref="P84" r:id="rId170"/>
-    <hyperlink ref="N85" r:id="rId171"/>
-    <hyperlink ref="P85" r:id="rId172"/>
-    <hyperlink ref="K86" r:id="rId173"/>
-    <hyperlink ref="N86" r:id="rId174"/>
-    <hyperlink ref="P86" r:id="rId175"/>
-    <hyperlink ref="K87" r:id="rId176"/>
-    <hyperlink ref="N87" r:id="rId177"/>
-    <hyperlink ref="P87" r:id="rId178"/>
-    <hyperlink ref="N88" r:id="rId179"/>
-    <hyperlink ref="P88" r:id="rId180"/>
-    <hyperlink ref="N89" r:id="rId181"/>
-    <hyperlink ref="P89" r:id="rId182"/>
-    <hyperlink ref="N90" r:id="rId183"/>
-    <hyperlink ref="P90" r:id="rId184"/>
-    <hyperlink ref="N91" r:id="rId185"/>
-    <hyperlink ref="P91" r:id="rId186"/>
-    <hyperlink ref="N92" r:id="rId187"/>
-    <hyperlink ref="P92" r:id="rId188"/>
-    <hyperlink ref="N93" r:id="rId189"/>
-    <hyperlink ref="P93" r:id="rId190"/>
-    <hyperlink ref="N94" r:id="rId191"/>
-    <hyperlink ref="P94" r:id="rId192"/>
-    <hyperlink ref="N95" r:id="rId193"/>
-    <hyperlink ref="P95" r:id="rId194"/>
-    <hyperlink ref="N96" r:id="rId195"/>
-    <hyperlink ref="P96" r:id="rId196"/>
-    <hyperlink ref="N97" r:id="rId197"/>
-    <hyperlink ref="P97" r:id="rId198"/>
-    <hyperlink ref="N98" r:id="rId199"/>
-    <hyperlink ref="P98" r:id="rId200"/>
-    <hyperlink ref="N99" r:id="rId201"/>
-    <hyperlink ref="P99" r:id="rId202"/>
-    <hyperlink ref="N100" r:id="rId203"/>
-    <hyperlink ref="P100" r:id="rId204"/>
-    <hyperlink ref="K101" r:id="rId205"/>
-    <hyperlink ref="N101" r:id="rId206"/>
-    <hyperlink ref="P101" r:id="rId207"/>
-    <hyperlink ref="N102" r:id="rId208"/>
-    <hyperlink ref="P102" r:id="rId209"/>
-    <hyperlink ref="N103" r:id="rId210"/>
-    <hyperlink ref="P103" r:id="rId211"/>
-    <hyperlink ref="N104" r:id="rId212"/>
-    <hyperlink ref="P104" r:id="rId213"/>
-    <hyperlink ref="N105" r:id="rId214"/>
-    <hyperlink ref="P105" r:id="rId215"/>
-    <hyperlink ref="N106" r:id="rId216"/>
-    <hyperlink ref="P106" r:id="rId217"/>
-    <hyperlink ref="N107" r:id="rId218"/>
-    <hyperlink ref="P107" r:id="rId219"/>
-    <hyperlink ref="N108" r:id="rId220"/>
-    <hyperlink ref="P108" r:id="rId221"/>
-    <hyperlink ref="N109" r:id="rId222"/>
-    <hyperlink ref="P109" r:id="rId223"/>
-    <hyperlink ref="N110" r:id="rId224"/>
-    <hyperlink ref="P110" r:id="rId225"/>
-    <hyperlink ref="N111" r:id="rId226"/>
-    <hyperlink ref="P111" r:id="rId227"/>
-    <hyperlink ref="N112" r:id="rId228"/>
-    <hyperlink ref="P112" r:id="rId229"/>
-    <hyperlink ref="N113" r:id="rId230"/>
-    <hyperlink ref="P113" r:id="rId231"/>
-    <hyperlink ref="N114" r:id="rId232"/>
-    <hyperlink ref="P114" r:id="rId233"/>
-    <hyperlink ref="N115" r:id="rId234"/>
-    <hyperlink ref="P115" r:id="rId235"/>
-    <hyperlink ref="N116" r:id="rId236"/>
-    <hyperlink ref="N117" r:id="rId237"/>
-    <hyperlink ref="N118" r:id="rId238"/>
-    <hyperlink ref="N119" r:id="rId239"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="P2" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N3" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="P3" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N4" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="P4" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N5" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="P5" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N6" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N7" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N8" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="K9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N9" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="K10" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="P10" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K11" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N11" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="P11" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="K12" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N12" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="P12" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N13" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="P13" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K14" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N14" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="P14" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N15" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="P15" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N16" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="P16" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N17" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="P17" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N18" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="P18" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N19" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="P19" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="N20" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="P20" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N21" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="P21" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="N22" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="P22" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N23" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="P23" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="N24" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="P24" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="N25" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="P25" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N26" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="P26" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="P27" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="N28" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="P28" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="N29" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="P29" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="N30" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="P30" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="N31" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="P31" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="N32" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="P32" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="N33" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="P33" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="N34" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="P34" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="N35" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="P35" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="N36" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="P36" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="N37" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="P37" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="N38" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="P38" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="N39" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="P39" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="N40" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="P40" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="N41" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="P41" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="N42" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="P42" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="N43" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="P43" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="N44" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="P44" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="N45" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="P45" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="N46" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="P46" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="N47" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="P47" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="N48" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="P48" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="N49" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="P49" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="K50" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="N50" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="P50" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="K51" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="N51" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="P51" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="N52" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="P52" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="N53" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="P53" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="N54" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="P54" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="N55" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="P55" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="N56" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="P56" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="N57" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="P57" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="N58" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="P58" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="N59" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="P59" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="N60" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="P60" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="N61" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="P61" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="N62" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="P62" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="N63" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="P63" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="N64" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="P64" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="N65" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="P65" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="N66" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="N67" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="N68" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="P68" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="N69" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="P69" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="N70" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="P70" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="N71" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="P71" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="N72" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="P72" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="N73" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="P73" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="N74" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="P74" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="N75" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="P75" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="N76" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="P76" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="N77" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="P77" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="N78" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="P78" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="N79" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="P79" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="N80" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="P80" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="N81" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="P81" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="N82" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="P82" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="N83" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="P83" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="N84" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="P84" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="N85" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="P85" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="K86" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="N86" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="P86" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="K87" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="N87" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="P87" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="N88" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="P88" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="N89" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="P89" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="N90" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="P90" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="N91" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="P91" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="N92" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="P92" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="N93" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="P93" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="N94" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="P94" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="N95" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="P95" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="N96" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="P96" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="N97" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="P97" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="N98" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="P98" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="N99" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="P99" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="N100" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="P100" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="K101" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="N101" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="P101" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="N102" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="P102" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="N103" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="P103" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="N104" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="P104" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="N105" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="P105" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="N106" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="P106" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="N107" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="P107" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="N108" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="P108" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="N109" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="P109" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="N110" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="P110" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="N111" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="P111" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="N112" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="P112" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="N113" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="P113" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="N114" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="P114" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="N115" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="P115" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="N116" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="N117" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="N118" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="N119" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="N27" r:id="rId239" xr:uid="{9EEC5597-2091-436B-ADE0-BE286A08243E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-14e.xlsx
+++ b/quizzes/peinture-14e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9323194-65B9-4CAE-92D9-5CB0F879AC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A6B0D9-179C-4DED-967B-ADCD3D7CE322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="606">
   <si>
     <t>Prénom</t>
   </si>
@@ -445,24 +445,6 @@
     <t>Museo dell'Opera del Duomo</t>
   </si>
   <si>
-    <t>Frick Collection, New York</t>
-  </si>
-  <si>
-    <t>National Gallery of Art, Washington</t>
-  </si>
-  <si>
-    <t>Museo dell'Opera del Duomo, Sienne</t>
-  </si>
-  <si>
-    <t>Museo Thyssen-Bornemisza, Madrid</t>
-  </si>
-  <si>
-    <t>National Gallery, Londres</t>
-  </si>
-  <si>
-    <t>Kimbell Art Museum, Fort Worth</t>
-  </si>
-  <si>
     <t>Église Santa Croce</t>
   </si>
   <si>
@@ -472,33 +454,21 @@
     <t>Pinacoteca Nazionale, Sienne</t>
   </si>
   <si>
-    <t>Galerie des Offices, Florence</t>
-  </si>
-  <si>
     <t>Museo Diocesano d'Arte Sacra, Sienne</t>
   </si>
   <si>
     <t>Basilique San Francesco, Sienne</t>
   </si>
   <si>
-    <t>Palazzo Comunale, Massa Marittima</t>
-  </si>
-  <si>
     <t>Palazzo Pubblico</t>
   </si>
   <si>
-    <t>Pieve di Santa Maria, Arezzo</t>
-  </si>
-  <si>
     <t>National Gallery</t>
   </si>
   <si>
     <t>Basilique inférieure de San Francesco, Assise</t>
   </si>
   <si>
-    <t>Basilique de San Francesco, Assise (collection privée)</t>
-  </si>
-  <si>
     <t>Galerie des Offices</t>
   </si>
   <si>
@@ -526,15 +496,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Cityscape_of_Siena_03.JPG/1280px-Cityscape_of_Siena_03.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Sacristie</t>
-  </si>
-  <si>
-    <t>Chapelle San Giacomo</t>
-  </si>
-  <si>
-    <t>Coupole du baptistère</t>
-  </si>
-  <si>
     <t xml:space="preserve">Le mur du fond de la Chapelle des Espagnols </t>
   </si>
   <si>
@@ -1841,6 +1802,42 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c7/Giotto_di_Bondone_-_No._14_Annunciation_-_The_Angel_Gabriel_Sent_by_God_-_WGA09190.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Frick Collection</t>
+  </si>
+  <si>
+    <t>National Gallery of Art</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Museo Thyssen-Bornemisza</t>
+  </si>
+  <si>
+    <t>Madrid</t>
+  </si>
+  <si>
+    <t>Kimbell Art Museum</t>
+  </si>
+  <si>
+    <t>Fort Worth</t>
+  </si>
+  <si>
+    <t>Pinacoteca Nazionale</t>
+  </si>
+  <si>
+    <t>Pieve di Santa Maria</t>
+  </si>
+  <si>
+    <t>Basilique inférieure de San Francesco</t>
+  </si>
+  <si>
+    <t>Basilique San Francesco</t>
+  </si>
+  <si>
+    <t>Basilique de San Francesco</t>
   </si>
 </sst>
 </file>
@@ -2198,6 +2195,9 @@
   <dimension ref="A1:X108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" customWidth="1"/>
+    <col min="12" max="12" width="32.140625" customWidth="1"/>
     <col min="13" max="13" width="41.28515625" customWidth="1"/>
     <col min="16" max="16" width="38.42578125" customWidth="1"/>
   </cols>
@@ -2302,37 +2302,34 @@
         <v>132</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L2" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="M2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="O2" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="Q2" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="S2" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T2" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U2" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="W2" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X2">
         <v>2</v>
@@ -2361,37 +2358,34 @@
         <v>132</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="L3" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="M3" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="O3" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="Q3" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="S3" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T3" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U3" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="W3" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X3">
         <v>2</v>
@@ -2414,28 +2408,28 @@
         <v>133</v>
       </c>
       <c r="M4" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="O4" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="S4" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T4" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="U4" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="W4" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="X4">
         <v>3</v>
@@ -2458,28 +2452,28 @@
         <v>133</v>
       </c>
       <c r="M5" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="O5" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="S5" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T5" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="U5" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="W5" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="X5">
         <v>3</v>
@@ -2508,28 +2502,28 @@
         <v>134</v>
       </c>
       <c r="M6" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="O6" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="Q6" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="S6" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T6" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="U6" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="W6" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X6">
         <v>3</v>
@@ -2557,20 +2551,17 @@
       <c r="J7" t="s">
         <v>135</v>
       </c>
-      <c r="L7" t="s">
-        <v>169</v>
-      </c>
       <c r="M7" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="S7" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="W7" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X7">
         <v>3</v>
@@ -2599,25 +2590,25 @@
         <v>136</v>
       </c>
       <c r="M8" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="Q8" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="S8" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T8" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="U8" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="W8" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X8">
         <v>3</v>
@@ -2643,25 +2634,22 @@
         <v>137</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="L9" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="M9" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="Q9" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="S9" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="W9" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X9">
         <v>3</v>
@@ -2687,31 +2675,31 @@
         <v>138</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L10" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="M10" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="S10" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T10" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="U10" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="W10" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X10">
         <v>3</v>
@@ -2737,31 +2725,31 @@
         <v>138</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L11" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="M11" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="S11" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T11" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="U11" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="W11" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X11">
         <v>3</v>
@@ -2787,31 +2775,31 @@
         <v>138</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="S12" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T12" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="U12" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="W12" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X12">
         <v>3</v>
@@ -2843,31 +2831,31 @@
         <v>139</v>
       </c>
       <c r="M13" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="O13" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q13" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="S13" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T13" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U13" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W13" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X13">
         <v>1</v>
@@ -2899,37 +2887,37 @@
         <v>139</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="L14" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="O14" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q14" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="S14" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T14" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U14" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W14" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X14">
         <v>1</v>
@@ -2961,34 +2949,34 @@
         <v>139</v>
       </c>
       <c r="L15" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="M15" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="O15" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q15" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="S15" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T15" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U15" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W15" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -3020,34 +3008,34 @@
         <v>139</v>
       </c>
       <c r="L16" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="M16" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="O16" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="P16" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q16" t="s">
         <v>443</v>
       </c>
-      <c r="Q16" t="s">
-        <v>456</v>
-      </c>
       <c r="S16" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T16" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U16" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W16" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -3079,34 +3067,34 @@
         <v>139</v>
       </c>
       <c r="L17" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="M17" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="O17" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q17" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="S17" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T17" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U17" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W17" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X17">
         <v>1</v>
@@ -3138,34 +3126,34 @@
         <v>139</v>
       </c>
       <c r="L18" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="M18" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="O18" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q18" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="S18" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T18" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U18" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W18" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X18">
         <v>1</v>
@@ -3197,34 +3185,34 @@
         <v>139</v>
       </c>
       <c r="L19" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="M19" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="O19" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q19" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="S19" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T19" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U19" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W19" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X19">
         <v>1</v>
@@ -3256,34 +3244,34 @@
         <v>139</v>
       </c>
       <c r="L20" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="M20" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="O20" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q20" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="S20" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T20" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U20" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W20" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X20">
         <v>1</v>
@@ -3315,34 +3303,34 @@
         <v>139</v>
       </c>
       <c r="L21" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="M21" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="O21" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q21" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="S21" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T21" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U21" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W21" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X21">
         <v>1</v>
@@ -3374,34 +3362,34 @@
         <v>139</v>
       </c>
       <c r="L22" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="M22" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="O22" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q22" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="S22" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T22" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U22" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W22" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -3433,34 +3421,34 @@
         <v>139</v>
       </c>
       <c r="L23" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="M23" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="O23" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q23" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="S23" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T23" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U23" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W23" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X23">
         <v>1</v>
@@ -3492,34 +3480,34 @@
         <v>139</v>
       </c>
       <c r="L24" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="M24" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="O24" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q24" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="S24" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T24" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U24" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W24" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X24">
         <v>1</v>
@@ -3551,34 +3539,34 @@
         <v>139</v>
       </c>
       <c r="L25" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="M25" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="O25" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q25" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="S25" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T25" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U25" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W25" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X25">
         <v>1</v>
@@ -3610,34 +3598,34 @@
         <v>139</v>
       </c>
       <c r="L26" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="M26" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="O26" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q26" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="S26" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T26" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U26" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W26" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X26">
         <v>1</v>
@@ -3669,34 +3657,34 @@
         <v>139</v>
       </c>
       <c r="L27" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="M27" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="O27" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q27" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="S27" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T27" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U27" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W27" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X27">
         <v>1</v>
@@ -3728,34 +3716,37 @@
         <v>139</v>
       </c>
       <c r="L28" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="M28" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="O28" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q28" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="S28" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T28" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U28" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W28" t="s">
-        <v>601</v>
+        <v>588</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -3784,34 +3775,34 @@
         <v>139</v>
       </c>
       <c r="L29" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="M29" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="O29" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q29" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="S29" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T29" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U29" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W29" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X29">
         <v>1</v>
@@ -3843,34 +3834,34 @@
         <v>139</v>
       </c>
       <c r="L30" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="M30" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="O30" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q30" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="S30" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T30" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U30" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W30" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X30">
         <v>1</v>
@@ -3902,34 +3893,34 @@
         <v>139</v>
       </c>
       <c r="L31" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="M31" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="O31" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q31" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="S31" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T31" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U31" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W31" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X31">
         <v>1</v>
@@ -3961,34 +3952,34 @@
         <v>139</v>
       </c>
       <c r="L32" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="M32" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="O32" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q32" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="S32" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T32" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U32" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W32" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X32">
         <v>1</v>
@@ -4020,34 +4011,34 @@
         <v>139</v>
       </c>
       <c r="L33" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="M33" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="O33" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q33" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="S33" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T33" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U33" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W33" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X33">
         <v>1</v>
@@ -4079,34 +4070,34 @@
         <v>139</v>
       </c>
       <c r="L34" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="M34" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="O34" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q34" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="S34" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T34" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U34" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W34" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -4138,34 +4129,34 @@
         <v>139</v>
       </c>
       <c r="L35" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="M35" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="O35" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q35" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="S35" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T35" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U35" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W35" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X35">
         <v>1</v>
@@ -4197,34 +4188,34 @@
         <v>139</v>
       </c>
       <c r="L36" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="M36" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="O36" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q36" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="S36" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T36" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U36" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W36" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X36">
         <v>1</v>
@@ -4256,34 +4247,34 @@
         <v>139</v>
       </c>
       <c r="L37" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="M37" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="O37" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q37" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="S37" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T37" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U37" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W37" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X37">
         <v>1</v>
@@ -4315,34 +4306,34 @@
         <v>139</v>
       </c>
       <c r="L38" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="M38" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="O38" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q38" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="S38" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T38" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U38" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W38" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X38">
         <v>1</v>
@@ -4374,34 +4365,34 @@
         <v>139</v>
       </c>
       <c r="L39" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="M39" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="O39" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q39" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="S39" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T39" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U39" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W39" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X39">
         <v>1</v>
@@ -4433,34 +4424,34 @@
         <v>139</v>
       </c>
       <c r="L40" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="M40" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="O40" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q40" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="S40" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T40" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U40" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W40" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X40">
         <v>1</v>
@@ -4492,34 +4483,34 @@
         <v>139</v>
       </c>
       <c r="L41" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="M41" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="O41" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q41" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="S41" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T41" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="U41" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="W41" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X41">
         <v>1</v>
@@ -4551,34 +4542,34 @@
         <v>139</v>
       </c>
       <c r="L42" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="M42" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="O42" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q42" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="S42" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T42" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U42" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W42" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X42">
         <v>1</v>
@@ -4610,34 +4601,34 @@
         <v>139</v>
       </c>
       <c r="L43" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="M43" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="O43" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q43" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="S43" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T43" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U43" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W43" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X43">
         <v>1</v>
@@ -4669,34 +4660,34 @@
         <v>139</v>
       </c>
       <c r="L44" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="M44" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="O44" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q44" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="S44" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T44" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U44" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W44" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X44">
         <v>1</v>
@@ -4728,34 +4719,34 @@
         <v>139</v>
       </c>
       <c r="L45" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="M45" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="O45" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q45" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="S45" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T45" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U45" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W45" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X45">
         <v>1</v>
@@ -4787,34 +4778,34 @@
         <v>139</v>
       </c>
       <c r="L46" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="M46" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="O46" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q46" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="S46" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T46" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U46" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W46" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X46">
         <v>1</v>
@@ -4846,34 +4837,34 @@
         <v>139</v>
       </c>
       <c r="L47" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="M47" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="O47" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q47" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="S47" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T47" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U47" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W47" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X47">
         <v>1</v>
@@ -4905,34 +4896,34 @@
         <v>139</v>
       </c>
       <c r="L48" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="M48" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="O48" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q48" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="S48" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T48" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U48" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W48" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X48">
         <v>1</v>
@@ -4964,34 +4955,34 @@
         <v>139</v>
       </c>
       <c r="L49" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="M49" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="O49" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q49" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="S49" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T49" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U49" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W49" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X49">
         <v>1</v>
@@ -5023,37 +5014,37 @@
         <v>139</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L50" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="M50" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="O50" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q50" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="S50" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T50" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U50" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W50" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X50">
         <v>1</v>
@@ -5085,37 +5076,37 @@
         <v>139</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L51" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="M51" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="O51" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q51" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="S51" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T51" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U51" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="W51" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X51">
         <v>1</v>
@@ -5147,34 +5138,34 @@
         <v>139</v>
       </c>
       <c r="L52" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="M52" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="O52" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q52" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="S52" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T52" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U52" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W52" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -5206,34 +5197,34 @@
         <v>139</v>
       </c>
       <c r="L53" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="M53" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="O53" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q53" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="S53" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T53" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U53" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W53" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X53">
         <v>1</v>
@@ -5265,34 +5256,34 @@
         <v>139</v>
       </c>
       <c r="L54" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="M54" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="O54" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q54" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="S54" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T54" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U54" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W54" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X54">
         <v>1</v>
@@ -5324,34 +5315,34 @@
         <v>139</v>
       </c>
       <c r="L55" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="M55" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="O55" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q55" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="S55" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T55" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U55" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W55" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X55">
         <v>1</v>
@@ -5383,34 +5374,34 @@
         <v>139</v>
       </c>
       <c r="L56" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="M56" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="O56" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q56" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="S56" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T56" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U56" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W56" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X56">
         <v>1</v>
@@ -5442,34 +5433,34 @@
         <v>139</v>
       </c>
       <c r="L57" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="M57" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="O57" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q57" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="S57" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T57" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U57" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W57" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X57">
         <v>1</v>
@@ -5501,34 +5492,34 @@
         <v>139</v>
       </c>
       <c r="L58" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="M58" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="O58" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q58" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="S58" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T58" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U58" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W58" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X58">
         <v>1</v>
@@ -5560,34 +5551,34 @@
         <v>139</v>
       </c>
       <c r="L59" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="M59" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="O59" t="s">
+        <v>417</v>
+      </c>
+      <c r="P59" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="P59" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="Q59" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="S59" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T59" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U59" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W59" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X59">
         <v>1</v>
@@ -5619,34 +5610,34 @@
         <v>139</v>
       </c>
       <c r="L60" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="M60" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="O60" t="s">
+        <v>417</v>
+      </c>
+      <c r="P60" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="P60" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="Q60" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="S60" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T60" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U60" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W60" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X60">
         <v>1</v>
@@ -5678,34 +5669,34 @@
         <v>139</v>
       </c>
       <c r="L61" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="M61" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="O61" t="s">
+        <v>417</v>
+      </c>
+      <c r="P61" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="P61" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="Q61" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="S61" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T61" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U61" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W61" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X61">
         <v>1</v>
@@ -5737,34 +5728,34 @@
         <v>139</v>
       </c>
       <c r="L62" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="M62" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="O62" t="s">
+        <v>417</v>
+      </c>
+      <c r="P62" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="P62" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="Q62" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="S62" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T62" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U62" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W62" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X62">
         <v>1</v>
@@ -5796,34 +5787,34 @@
         <v>139</v>
       </c>
       <c r="L63" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="M63" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="O63" t="s">
+        <v>417</v>
+      </c>
+      <c r="P63" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="P63" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="Q63" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="S63" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T63" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U63" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W63" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X63">
         <v>1</v>
@@ -5855,34 +5846,34 @@
         <v>139</v>
       </c>
       <c r="L64" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="M64" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="O64" t="s">
+        <v>417</v>
+      </c>
+      <c r="P64" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="P64" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="Q64" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="S64" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T64" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U64" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W64" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X64">
         <v>1</v>
@@ -5914,34 +5905,34 @@
         <v>139</v>
       </c>
       <c r="L65" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="M65" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="O65" t="s">
+        <v>417</v>
+      </c>
+      <c r="P65" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="P65" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="Q65" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="S65" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T65" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="U65" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="W65" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X65">
         <v>1</v>
@@ -5973,31 +5964,31 @@
         <v>139</v>
       </c>
       <c r="L66" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="M66" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="O66" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="Q66" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="S66" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T66" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="U66" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="W66" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X66">
         <v>1</v>
@@ -6029,25 +6020,25 @@
         <v>140</v>
       </c>
       <c r="M67" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="Q67" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="S67" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T67" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="U67" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="W67" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X67">
         <v>1</v>
@@ -6079,31 +6070,31 @@
         <v>140</v>
       </c>
       <c r="M68" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="O68" t="s">
+        <v>418</v>
+      </c>
+      <c r="P68" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P68" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="Q68" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="S68" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T68" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="U68" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="W68" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X68">
         <v>1</v>
@@ -6129,37 +6120,37 @@
         <v>96</v>
       </c>
       <c r="I69" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="J69" t="s">
-        <v>141</v>
+        <v>594</v>
       </c>
       <c r="M69" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="O69" t="s">
+        <v>418</v>
+      </c>
+      <c r="P69" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P69" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="Q69" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="S69" t="s">
+        <v>522</v>
+      </c>
+      <c r="T69" t="s">
         <v>535</v>
       </c>
-      <c r="T69" t="s">
-        <v>548</v>
-      </c>
       <c r="U69" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="W69" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X69">
         <v>1</v>
@@ -6185,37 +6176,37 @@
         <v>96</v>
       </c>
       <c r="I70" t="s">
-        <v>123</v>
+        <v>596</v>
       </c>
       <c r="J70" t="s">
-        <v>142</v>
+        <v>595</v>
       </c>
       <c r="M70" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="O70" t="s">
+        <v>418</v>
+      </c>
+      <c r="P70" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P70" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="Q70" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="S70" t="s">
+        <v>522</v>
+      </c>
+      <c r="T70" t="s">
         <v>535</v>
       </c>
-      <c r="T70" t="s">
-        <v>548</v>
-      </c>
       <c r="U70" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="W70" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X70">
         <v>1</v>
@@ -6244,34 +6235,34 @@
         <v>123</v>
       </c>
       <c r="J71" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="M71" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="O71" t="s">
+        <v>418</v>
+      </c>
+      <c r="P71" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P71" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="Q71" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="S71" t="s">
+        <v>522</v>
+      </c>
+      <c r="T71" t="s">
         <v>535</v>
       </c>
-      <c r="T71" t="s">
-        <v>548</v>
-      </c>
       <c r="U71" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="W71" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X71">
         <v>1</v>
@@ -6297,37 +6288,37 @@
         <v>96</v>
       </c>
       <c r="I72" t="s">
-        <v>123</v>
+        <v>598</v>
       </c>
       <c r="J72" t="s">
-        <v>144</v>
+        <v>597</v>
       </c>
       <c r="M72" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="O72" t="s">
+        <v>418</v>
+      </c>
+      <c r="P72" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P72" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="Q72" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="S72" t="s">
+        <v>522</v>
+      </c>
+      <c r="T72" t="s">
         <v>535</v>
       </c>
-      <c r="T72" t="s">
-        <v>548</v>
-      </c>
       <c r="U72" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="W72" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X72">
         <v>1</v>
@@ -6353,37 +6344,37 @@
         <v>96</v>
       </c>
       <c r="I73" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J73" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M73" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="O73" t="s">
+        <v>418</v>
+      </c>
+      <c r="P73" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P73" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="Q73" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="S73" t="s">
+        <v>522</v>
+      </c>
+      <c r="T73" t="s">
         <v>535</v>
       </c>
-      <c r="T73" t="s">
-        <v>548</v>
-      </c>
       <c r="U73" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="W73" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X73">
         <v>1</v>
@@ -6409,37 +6400,37 @@
         <v>96</v>
       </c>
       <c r="I74" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J74" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M74" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="O74" t="s">
+        <v>418</v>
+      </c>
+      <c r="P74" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P74" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="Q74" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="S74" t="s">
+        <v>522</v>
+      </c>
+      <c r="T74" t="s">
         <v>535</v>
       </c>
-      <c r="T74" t="s">
-        <v>548</v>
-      </c>
       <c r="U74" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="W74" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X74">
         <v>1</v>
@@ -6465,37 +6456,37 @@
         <v>96</v>
       </c>
       <c r="I75" t="s">
-        <v>123</v>
+        <v>600</v>
       </c>
       <c r="J75" t="s">
-        <v>146</v>
+        <v>599</v>
       </c>
       <c r="M75" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="O75" t="s">
+        <v>418</v>
+      </c>
+      <c r="P75" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P75" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="Q75" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="S75" t="s">
+        <v>522</v>
+      </c>
+      <c r="T75" t="s">
         <v>535</v>
       </c>
-      <c r="T75" t="s">
-        <v>548</v>
-      </c>
       <c r="U75" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="W75" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X75">
         <v>1</v>
@@ -6530,28 +6521,28 @@
         <v>138</v>
       </c>
       <c r="M76" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q76" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="S76" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T76" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="U76" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="W76" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X76">
         <v>1</v>
@@ -6574,31 +6565,31 @@
         <v>138</v>
       </c>
       <c r="L77" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="M77" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q77" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="S77" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T77" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="U77" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="W77" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X77">
         <v>1</v>
@@ -6624,31 +6615,31 @@
         <v>119</v>
       </c>
       <c r="J78" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="L78" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="M78" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="S78" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T78" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="U78" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="W78" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X78">
         <v>2</v>
@@ -6674,31 +6665,31 @@
         <v>123</v>
       </c>
       <c r="J79" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="M79" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q79" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="S79" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T79" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="U79" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="W79" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X79">
         <v>1</v>
@@ -6724,31 +6715,31 @@
         <v>123</v>
       </c>
       <c r="J80" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M80" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q80" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="S80" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T80" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="U80" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="W80" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X80">
         <v>1</v>
@@ -6774,31 +6765,31 @@
         <v>119</v>
       </c>
       <c r="J81" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M81" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="O81" t="s">
+        <v>419</v>
+      </c>
+      <c r="P81" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="P81" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="Q81" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="S81" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="U81" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="W81" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X81">
         <v>1</v>
@@ -6824,31 +6815,31 @@
         <v>119</v>
       </c>
       <c r="J82" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M82" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q82" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="S82" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="T82" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="U82" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="W82" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X82">
         <v>1</v>
@@ -6871,34 +6862,34 @@
         <v>103</v>
       </c>
       <c r="I83" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J83" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M83" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q83" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="S83" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T83" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="U83" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="W83" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X83">
         <v>1</v>
@@ -6924,31 +6915,31 @@
         <v>123</v>
       </c>
       <c r="J84" t="s">
-        <v>149</v>
+        <v>601</v>
       </c>
       <c r="M84" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q84" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="S84" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="T84" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="U84" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="W84" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X84">
         <v>1</v>
@@ -6974,31 +6965,31 @@
         <v>123</v>
       </c>
       <c r="J85" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="M85" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q85" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="S85" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T85" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="U85" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="W85" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X85">
         <v>1</v>
@@ -7024,34 +7015,34 @@
         <v>123</v>
       </c>
       <c r="J86" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="M86" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="O86" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="S86" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T86" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="U86" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="W86" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X86">
         <v>1</v>
@@ -7077,34 +7068,34 @@
         <v>123</v>
       </c>
       <c r="J87" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="M87" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="O87" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="S87" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T87" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="U87" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="W87" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X87">
         <v>1</v>
@@ -7130,31 +7121,31 @@
         <v>124</v>
       </c>
       <c r="J88" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="M88" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q88" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="S88" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T88" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="U88" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="W88" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X88">
         <v>1</v>
@@ -7180,37 +7171,37 @@
         <v>123</v>
       </c>
       <c r="J89" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="L89" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="M89" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="O89" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="Q89" t="s">
+        <v>510</v>
+      </c>
+      <c r="S89" t="s">
         <v>523</v>
       </c>
-      <c r="S89" t="s">
-        <v>536</v>
-      </c>
       <c r="T89" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U89" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="W89" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X89">
         <v>1</v>
@@ -7236,37 +7227,37 @@
         <v>123</v>
       </c>
       <c r="J90" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="L90" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="M90" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="O90" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="Q90" t="s">
+        <v>510</v>
+      </c>
+      <c r="S90" t="s">
         <v>523</v>
       </c>
-      <c r="S90" t="s">
-        <v>536</v>
-      </c>
       <c r="T90" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U90" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="W90" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X90">
         <v>1</v>
@@ -7292,37 +7283,37 @@
         <v>123</v>
       </c>
       <c r="J91" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="L91" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="M91" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="O91" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="Q91" t="s">
+        <v>510</v>
+      </c>
+      <c r="S91" t="s">
         <v>523</v>
       </c>
-      <c r="S91" t="s">
-        <v>536</v>
-      </c>
       <c r="T91" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U91" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="W91" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X91">
         <v>1</v>
@@ -7348,37 +7339,37 @@
         <v>123</v>
       </c>
       <c r="J92" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="L92" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="M92" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="O92" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="Q92" t="s">
+        <v>510</v>
+      </c>
+      <c r="S92" t="s">
         <v>523</v>
       </c>
-      <c r="S92" t="s">
-        <v>536</v>
-      </c>
       <c r="T92" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="U92" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="W92" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X92">
         <v>1</v>
@@ -7404,31 +7395,31 @@
         <v>125</v>
       </c>
       <c r="J93" t="s">
-        <v>155</v>
+        <v>602</v>
       </c>
       <c r="M93" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q93" t="s">
+        <v>511</v>
+      </c>
+      <c r="S93" t="s">
         <v>524</v>
       </c>
-      <c r="S93" t="s">
-        <v>537</v>
-      </c>
       <c r="T93" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="U93" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="W93" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X93">
         <v>1</v>
@@ -7454,34 +7445,34 @@
         <v>123</v>
       </c>
       <c r="J94" t="s">
-        <v>149</v>
+        <v>601</v>
       </c>
       <c r="M94" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="O94" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="Q94" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="S94" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T94" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="U94" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="W94" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X94">
         <v>1</v>
@@ -7507,34 +7498,34 @@
         <v>119</v>
       </c>
       <c r="J95" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M95" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="O95" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="Q95" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="S95" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T95" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="U95" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="W95" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X95">
         <v>1</v>
@@ -7563,28 +7554,28 @@
         <v>140</v>
       </c>
       <c r="M96" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q96" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="S96" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T96" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="U96" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="W96" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X96">
         <v>1</v>
@@ -7610,34 +7601,34 @@
         <v>126</v>
       </c>
       <c r="J97" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="M97" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="O97" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="Q97" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="S97" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T97" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="U97" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="W97" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X97">
         <v>1</v>
@@ -7666,28 +7657,28 @@
         <v>140</v>
       </c>
       <c r="M98" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q98" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="S98" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T98" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="U98" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="W98" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X98">
         <v>1</v>
@@ -7713,34 +7704,34 @@
         <v>127</v>
       </c>
       <c r="J99" t="s">
-        <v>157</v>
+        <v>603</v>
       </c>
       <c r="M99" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="O99" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="Q99" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="S99" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T99" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="U99" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="W99" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X99">
         <v>1</v>
@@ -7766,34 +7757,34 @@
         <v>127</v>
       </c>
       <c r="J100" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="M100" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="O100" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="P100" s="1" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="Q100" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="S100" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T100" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="U100" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="W100" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X100">
         <v>1</v>
@@ -7816,37 +7807,37 @@
         <v>104</v>
       </c>
       <c r="I101" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J101" t="s">
-        <v>152</v>
+        <v>604</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="M101" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="O101" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="S101" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T101" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="U101" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="W101" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X101">
         <v>1</v>
@@ -7872,28 +7863,28 @@
         <v>127</v>
       </c>
       <c r="J102" t="s">
-        <v>158</v>
+        <v>605</v>
       </c>
       <c r="M102" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="O102" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="Q102" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="S102" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="W102" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X102">
         <v>1</v>
@@ -7919,31 +7910,31 @@
         <v>119</v>
       </c>
       <c r="J103" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="M103" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="P103" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q103" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="S103" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="T103" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="U103" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="W103" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X103">
         <v>1</v>
@@ -7966,31 +7957,31 @@
         <v>128</v>
       </c>
       <c r="J104" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="M104" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="Q104" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="S104" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="T104" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="U104" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="W104" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X104">
         <v>1</v>
@@ -8013,22 +8004,22 @@
         <v>129</v>
       </c>
       <c r="J105" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="M105" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="O105" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="S105" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="W105" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="X105">
         <v>3</v>
@@ -8051,22 +8042,22 @@
         <v>130</v>
       </c>
       <c r="J106" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="M106" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="Q106" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="S106" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="W106" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="X106">
         <v>3</v>
@@ -8086,22 +8077,22 @@
         <v>131</v>
       </c>
       <c r="J107" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="M107" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="Q107" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="S107" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="W107" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="X107">
         <v>2</v>
@@ -8118,28 +8109,28 @@
         <v>126</v>
       </c>
       <c r="J108" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="M108" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="Q108" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="S108" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="T108" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="U108" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="W108" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="X108">
         <v>3</v>

--- a/quizzes/peinture-14e.xlsx
+++ b/quizzes/peinture-14e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B1FABE-6D47-40E6-BB3E-A4F3E5513CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA1A49F-7AE5-429B-90F4-CBB376CF3517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="613">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1465,9 +1465,6 @@
     <t>Assise</t>
   </si>
   <si>
-    <t>Basilique inférieure de San Francesco</t>
-  </si>
-  <si>
     <t>Déposition de croix</t>
   </si>
   <si>
@@ -1486,9 +1483,6 @@
     <t>1320 environ</t>
   </si>
   <si>
-    <t>Basilique inférieure de San Francesco, Assise</t>
-  </si>
-  <si>
     <t>Crucifixion</t>
   </si>
   <si>
@@ -1510,9 +1504,6 @@
     <t>1340 environ</t>
   </si>
   <si>
-    <t>Basilique de San Francesco</t>
-  </si>
-  <si>
     <t>Madone des couchers de soleil</t>
   </si>
   <si>
@@ -1613,9 +1604,6 @@
   </si>
   <si>
     <t>Vers 1312-1318</t>
-  </si>
-  <si>
-    <t>Basilique Saint-François</t>
   </si>
   <si>
     <t>Le Miracle de l'enfant ressuscité</t>
@@ -6134,7 +6122,7 @@
         <v>385</v>
       </c>
       <c r="R80" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="S80" t="s">
         <v>50</v>
@@ -6938,16 +6926,16 @@
         <v>480</v>
       </c>
       <c r="F98" t="s">
+        <v>491</v>
+      </c>
+      <c r="J98" t="s">
         <v>481</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>482</v>
       </c>
-      <c r="K98" t="s">
+      <c r="L98" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="M98" t="s">
         <v>456</v>
@@ -6962,10 +6950,10 @@
         <v>34</v>
       </c>
       <c r="T98" t="s">
+        <v>484</v>
+      </c>
+      <c r="U98" t="s">
         <v>485</v>
-      </c>
-      <c r="U98" t="s">
-        <v>486</v>
       </c>
       <c r="W98">
         <v>1</v>
@@ -6979,22 +6967,22 @@
         <v>364</v>
       </c>
       <c r="D99" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E99" t="s">
         <v>480</v>
       </c>
       <c r="F99" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="J99" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K99" t="s">
         <v>240</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="M99" t="s">
         <v>456</v>
@@ -7009,10 +6997,10 @@
         <v>34</v>
       </c>
       <c r="T99" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="U99" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="W99">
         <v>1</v>
@@ -7032,16 +7020,16 @@
         <v>480</v>
       </c>
       <c r="F100" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>245</v>
       </c>
       <c r="J100" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M100" t="s">
         <v>415</v>
@@ -7073,22 +7061,22 @@
         <v>364</v>
       </c>
       <c r="D101" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E101" t="s">
         <v>480</v>
       </c>
       <c r="F101" t="s">
+        <v>491</v>
+      </c>
+      <c r="J101" t="s">
+        <v>494</v>
+      </c>
+      <c r="K101" t="s">
+        <v>495</v>
+      </c>
+      <c r="L101" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="J101" t="s">
-        <v>497</v>
-      </c>
-      <c r="K101" t="s">
-        <v>498</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="M101" t="s">
         <v>456</v>
@@ -7111,10 +7099,10 @@
         <v>71</v>
       </c>
       <c r="B102" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D102" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E102" t="s">
         <v>26</v>
@@ -7123,13 +7111,13 @@
         <v>380</v>
       </c>
       <c r="J102" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="K102" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="N102" s="1"/>
       <c r="R102" t="s">
@@ -7139,10 +7127,10 @@
         <v>391</v>
       </c>
       <c r="T102" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="U102" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="W102">
         <v>1</v>
@@ -7151,7 +7139,7 @@
         <v>71</v>
       </c>
       <c r="Y102" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="103" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7159,10 +7147,10 @@
         <v>71</v>
       </c>
       <c r="B103" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D103" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E103" t="s">
         <v>304</v>
@@ -7177,7 +7165,7 @@
         <v>424</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="R103" t="s">
         <v>34</v>
@@ -7186,10 +7174,10 @@
         <v>34</v>
       </c>
       <c r="T103" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="U103" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="W103">
         <v>1</v>
@@ -7198,7 +7186,7 @@
         <v>71</v>
       </c>
       <c r="Y103" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="104" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7206,10 +7194,10 @@
         <v>71</v>
       </c>
       <c r="B104" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D104" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E104" t="s">
         <v>304</v>
@@ -7218,25 +7206,25 @@
         <v>429</v>
       </c>
       <c r="J104" t="s">
+        <v>509</v>
+      </c>
+      <c r="K104" t="s">
+        <v>510</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="R104" t="s">
+        <v>34</v>
+      </c>
+      <c r="S104" t="s">
+        <v>34</v>
+      </c>
+      <c r="T104" t="s">
         <v>512</v>
       </c>
-      <c r="K104" t="s">
+      <c r="U104" t="s">
         <v>513</v>
-      </c>
-      <c r="L104" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="R104" t="s">
-        <v>34</v>
-      </c>
-      <c r="S104" t="s">
-        <v>34</v>
-      </c>
-      <c r="T104" t="s">
-        <v>515</v>
-      </c>
-      <c r="U104" t="s">
-        <v>516</v>
       </c>
       <c r="W104">
         <v>1</v>
@@ -7245,7 +7233,7 @@
         <v>71</v>
       </c>
       <c r="Y104" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="105" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7253,25 +7241,25 @@
         <v>71</v>
       </c>
       <c r="B105" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D105" t="s">
+        <v>514</v>
+      </c>
+      <c r="E105" t="s">
+        <v>515</v>
+      </c>
+      <c r="F105" t="s">
+        <v>516</v>
+      </c>
+      <c r="J105" t="s">
         <v>517</v>
       </c>
-      <c r="E105" t="s">
+      <c r="K105" t="s">
         <v>518</v>
       </c>
-      <c r="F105" t="s">
+      <c r="L105" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="J105" t="s">
-        <v>520</v>
-      </c>
-      <c r="K105" t="s">
-        <v>521</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="R105" t="s">
         <v>49</v>
@@ -7283,7 +7271,7 @@
         <v>36</v>
       </c>
       <c r="U105" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="W105">
         <v>1</v>
@@ -7292,7 +7280,7 @@
         <v>71</v>
       </c>
       <c r="Y105" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="106" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7300,25 +7288,25 @@
         <v>71</v>
       </c>
       <c r="B106" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D106" t="s">
         <v>365</v>
       </c>
       <c r="E106" t="s">
+        <v>521</v>
+      </c>
+      <c r="F106" t="s">
+        <v>522</v>
+      </c>
+      <c r="J106" t="s">
+        <v>523</v>
+      </c>
+      <c r="K106" t="s">
         <v>524</v>
       </c>
-      <c r="F106" t="s">
+      <c r="L106" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="J106" t="s">
-        <v>526</v>
-      </c>
-      <c r="K106" t="s">
-        <v>527</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="R106" t="s">
         <v>450</v>
@@ -7330,7 +7318,7 @@
         <v>176</v>
       </c>
       <c r="U106" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="W106">
         <v>1</v>
@@ -7339,7 +7327,7 @@
         <v>71</v>
       </c>
       <c r="Y106" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="107" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7347,31 +7335,31 @@
         <v>71</v>
       </c>
       <c r="B107" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D107" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E107" t="s">
         <v>480</v>
       </c>
       <c r="F107" t="s">
+        <v>491</v>
+      </c>
+      <c r="J107" t="s">
+        <v>528</v>
+      </c>
+      <c r="K107" t="s">
+        <v>529</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="M107" t="s">
         <v>531</v>
       </c>
-      <c r="J107" t="s">
+      <c r="N107" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="K107" t="s">
-        <v>533</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="M107" t="s">
-        <v>535</v>
-      </c>
-      <c r="N107" s="1" t="s">
-        <v>536</v>
       </c>
       <c r="R107" t="s">
         <v>34</v>
@@ -7386,7 +7374,7 @@
         <v>71</v>
       </c>
       <c r="Y107" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="108" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7394,25 +7382,25 @@
         <v>71</v>
       </c>
       <c r="B108" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D108" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E108" t="s">
         <v>304</v>
       </c>
       <c r="F108" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="J108" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="K108" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="R108" t="s">
         <v>49</v>
@@ -7421,7 +7409,7 @@
         <v>391</v>
       </c>
       <c r="T108" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="U108" t="s">
         <v>398</v>
@@ -7433,7 +7421,7 @@
         <v>71</v>
       </c>
       <c r="Y108" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="109" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7441,25 +7429,25 @@
         <v>71</v>
       </c>
       <c r="B109" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D109" t="s">
         <v>394</v>
       </c>
       <c r="E109" t="s">
+        <v>539</v>
+      </c>
+      <c r="F109" t="s">
+        <v>540</v>
+      </c>
+      <c r="J109" t="s">
+        <v>541</v>
+      </c>
+      <c r="K109" t="s">
+        <v>542</v>
+      </c>
+      <c r="L109" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="F109" t="s">
-        <v>544</v>
-      </c>
-      <c r="J109" t="s">
-        <v>545</v>
-      </c>
-      <c r="K109" t="s">
-        <v>546</v>
-      </c>
-      <c r="L109" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="R109" t="s">
         <v>49</v>
@@ -7468,10 +7456,10 @@
         <v>391</v>
       </c>
       <c r="T109" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="U109" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="W109">
         <v>1</v>
@@ -7480,7 +7468,7 @@
         <v>71</v>
       </c>
       <c r="Y109" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="110" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7488,25 +7476,25 @@
         <v>71</v>
       </c>
       <c r="B110" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D110" t="s">
+        <v>546</v>
+      </c>
+      <c r="E110" t="s">
+        <v>547</v>
+      </c>
+      <c r="F110" t="s">
+        <v>548</v>
+      </c>
+      <c r="J110" t="s">
+        <v>549</v>
+      </c>
+      <c r="K110" t="s">
         <v>550</v>
       </c>
-      <c r="E110" t="s">
+      <c r="L110" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="F110" t="s">
-        <v>552</v>
-      </c>
-      <c r="J110" t="s">
-        <v>553</v>
-      </c>
-      <c r="K110" t="s">
-        <v>554</v>
-      </c>
-      <c r="L110" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="R110" t="s">
         <v>450</v>
@@ -7515,7 +7503,7 @@
         <v>391</v>
       </c>
       <c r="T110" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="U110" t="s">
         <v>398</v>
@@ -7527,7 +7515,7 @@
         <v>71</v>
       </c>
       <c r="Y110" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="111" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7535,25 +7523,25 @@
         <v>71</v>
       </c>
       <c r="B111" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D111" t="s">
+        <v>553</v>
+      </c>
+      <c r="E111" t="s">
+        <v>554</v>
+      </c>
+      <c r="F111" t="s">
+        <v>555</v>
+      </c>
+      <c r="J111" t="s">
+        <v>556</v>
+      </c>
+      <c r="K111" t="s">
         <v>557</v>
       </c>
-      <c r="E111" t="s">
+      <c r="L111" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="F111" t="s">
-        <v>559</v>
-      </c>
-      <c r="J111" t="s">
-        <v>560</v>
-      </c>
-      <c r="K111" t="s">
-        <v>561</v>
-      </c>
-      <c r="L111" s="2" t="s">
-        <v>562</v>
       </c>
       <c r="R111" t="s">
         <v>450</v>
@@ -7562,10 +7550,10 @@
         <v>391</v>
       </c>
       <c r="T111" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="U111" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="W111">
         <v>1</v>
@@ -7574,7 +7562,7 @@
         <v>71</v>
       </c>
       <c r="Y111" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="112" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7582,25 +7570,25 @@
         <v>71</v>
       </c>
       <c r="B112" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D112" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="E112" t="s">
         <v>26</v>
       </c>
       <c r="F112" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="J112" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="K112" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="R112" t="s">
         <v>49</v>
@@ -7609,7 +7597,7 @@
         <v>391</v>
       </c>
       <c r="T112" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="U112" t="s">
         <v>319</v>
@@ -7621,7 +7609,7 @@
         <v>71</v>
       </c>
       <c r="Y112" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="113" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7629,25 +7617,25 @@
         <v>71</v>
       </c>
       <c r="B113" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D113" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E113" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F113" t="s">
         <v>44</v>
       </c>
       <c r="J113" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="K113" t="s">
         <v>368</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="R113" t="s">
         <v>49</v>
@@ -7656,10 +7644,10 @@
         <v>391</v>
       </c>
       <c r="T113" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="U113" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="W113">
         <v>1</v>
@@ -7668,33 +7656,33 @@
         <v>71</v>
       </c>
       <c r="Y113" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B114" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D114" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E114" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F114" t="s">
         <v>422</v>
       </c>
       <c r="J114" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="K114" t="s">
         <v>307</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="N114" s="1" t="s">
         <v>128</v>
@@ -7706,10 +7694,10 @@
         <v>34</v>
       </c>
       <c r="T114" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="U114" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="W114">
         <v>1</v>
@@ -7717,34 +7705,34 @@
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B115" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="D115" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="E115" t="s">
         <v>313</v>
       </c>
       <c r="F115" t="s">
+        <v>583</v>
+      </c>
+      <c r="J115" t="s">
+        <v>584</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="M115" t="s">
+        <v>586</v>
+      </c>
+      <c r="R115" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="J115" t="s">
+      <c r="S115" t="s">
         <v>588</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="M115" t="s">
-        <v>590</v>
-      </c>
-      <c r="R115" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="S115" t="s">
-        <v>592</v>
       </c>
       <c r="W115">
         <v>3</v>
@@ -7752,28 +7740,28 @@
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>589</v>
+      </c>
+      <c r="B116" t="s">
+        <v>590</v>
+      </c>
+      <c r="D116" t="s">
+        <v>591</v>
+      </c>
+      <c r="E116" t="s">
+        <v>592</v>
+      </c>
+      <c r="F116" t="s">
         <v>593</v>
       </c>
-      <c r="B116" t="s">
+      <c r="J116" t="s">
         <v>594</v>
       </c>
-      <c r="D116" t="s">
+      <c r="K116" t="s">
         <v>595</v>
       </c>
-      <c r="E116" t="s">
+      <c r="L116" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="F116" t="s">
-        <v>597</v>
-      </c>
-      <c r="J116" t="s">
-        <v>598</v>
-      </c>
-      <c r="K116" t="s">
-        <v>599</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>600</v>
       </c>
       <c r="R116" t="s">
         <v>349</v>
@@ -7787,28 +7775,28 @@
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>597</v>
+      </c>
+      <c r="B117" t="s">
+        <v>598</v>
+      </c>
+      <c r="D117" t="s">
+        <v>599</v>
+      </c>
+      <c r="E117" t="s">
+        <v>600</v>
+      </c>
+      <c r="F117" t="s">
         <v>601</v>
       </c>
-      <c r="B117" t="s">
+      <c r="J117" t="s">
         <v>602</v>
       </c>
-      <c r="D117" t="s">
+      <c r="K117" t="s">
         <v>603</v>
       </c>
-      <c r="E117" t="s">
+      <c r="L117" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="F117" t="s">
-        <v>605</v>
-      </c>
-      <c r="J117" t="s">
-        <v>606</v>
-      </c>
-      <c r="K117" t="s">
-        <v>607</v>
-      </c>
-      <c r="L117" s="1" t="s">
-        <v>608</v>
       </c>
       <c r="R117" t="s">
         <v>349</v>
@@ -7822,10 +7810,10 @@
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C118" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="D118" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="E118" t="s">
         <v>332</v>
@@ -7834,16 +7822,16 @@
         <v>333</v>
       </c>
       <c r="J118" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="K118" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="R118" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="S118" t="s">
         <v>50</v>
@@ -7852,7 +7840,7 @@
         <v>386</v>
       </c>
       <c r="U118" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="W118">
         <v>3</v>
